--- a/artfynd/A 10484-2026 artfynd.xlsx
+++ b/artfynd/A 10484-2026 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>94109707</v>
+        <v>94109682</v>
       </c>
       <c r="B2" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -716,10 +711,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>583469.1431997162</v>
+        <v>583456</v>
       </c>
       <c r="R2" t="n">
-        <v>6741822.440388724</v>
+        <v>6741828</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -751,7 +746,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -761,7 +756,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,15 +783,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>94109682</v>
+        <v>94109707</v>
       </c>
       <c r="B3" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -829,10 +819,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>583456.2981773936</v>
+        <v>583469</v>
       </c>
       <c r="R3" t="n">
-        <v>6741827.999259856</v>
+        <v>6741822</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -864,7 +854,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -874,7 +864,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD3" t="b">
